--- a/FieldConfigrationFile.xlsx
+++ b/FieldConfigrationFile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prakhar\Desktop\Projects\IMGC Project\Field Level Mapping Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16286F94-EA9C-44A4-B7AB-D238A9D87D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A164DB-53E2-4CA1-A94A-BC4C3F14AC50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{02CFE6FC-DC13-4DF7-B179-54CE07624848}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="131">
   <si>
     <t>PAS Field Name</t>
   </si>
@@ -90,9 +90,6 @@
   </si>
   <si>
     <t>Loan_Type</t>
-  </si>
-  <si>
-    <t>Type_Of_Employment_Loan</t>
   </si>
   <si>
     <t>Foir</t>
@@ -210,12 +207,6 @@
     <t>In the Application Form, check the SOURCING CHANNEL DETAILS section under the field “Channel Name.” Update the PAS Field only if this value is present; otherwise, mark it as NA.</t>
   </si>
   <si>
-    <t>In the CAM Excel file, under the Basic Input sheet, the field “Customer Type” typically contains values such as Salaried, Self-Employed Non-Professional, and similar categories. This field can be found at the top.</t>
-  </si>
-  <si>
-    <t>In the PD (Word document), under the About Applicant or a similar section, you will find statements such as “The applicant is the proprietor of the firm M/S Om Construction” or other similar declarations.</t>
-  </si>
-  <si>
     <t>Anwhere, If mentioned in PD then make it as Yes, if nothing is mentioned then make it as No</t>
   </si>
   <si>
@@ -712,142 +703,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> HOME CONSTRUCTION LOAN,  PLOT HOME CONSTRUCTION LOAN among others.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>In the PD report, under the Applicant Details section, there is a</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> field</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> labeled “</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Profile</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>,” which generally contains values such as Salaried, among others.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">In the Application Form, under the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Occupation/Business Details</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> section, the field </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Salaried / Self-Employed”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> typically contains values such as </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Salaried</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SENP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, and other similar categories.</t>
     </r>
   </si>
   <si>
@@ -3818,53 +3673,6 @@
   </si>
   <si>
     <t>PD</t>
-  </si>
-  <si>
-    <r>
-      <t>In the PD (Word document), under the "</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>About Employment</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">" </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>section</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> or similar areas, look for keywords like "having cash salary" or comparable phrases/statements. Analyze these to determine whether the salary mode is cash or bank deposit.</t>
-    </r>
   </si>
   <si>
     <r>
@@ -4781,6 +4589,53 @@
 Example:
 Source: +91 8377998214
 Output: 8377998214</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>In the PD (Word document), under the "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>About Employment</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>section</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or similar areas, look for keywords like "having cash salary" or comparable phrases/statements. Analyze these to determine whether the salary mode is cash or SALARY REFLECTED IN BANK.</t>
     </r>
   </si>
 </sst>
@@ -4835,7 +4690,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4845,6 +4700,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4876,7 +4737,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4903,6 +4764,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5239,7 +5103,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3765008E-87C2-42DA-8C71-BC2650E30679}">
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" style="1" customWidth="1"/>
@@ -5263,19 +5127,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>46</v>
-      </c>
       <c r="D1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>67</v>
-      </c>
       <c r="F1" s="6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>1</v>
@@ -5307,32 +5171,32 @@
         <v>9</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C2" s="8">
         <v>30</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N2" s="9"/>
     </row>
@@ -5341,23 +5205,23 @@
         <v>10</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3" s="8">
         <v>25</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
       <c r="J3" s="9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
@@ -5369,32 +5233,32 @@
         <v>11</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C4" s="8">
         <v>25</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
       <c r="I4" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K4" s="9"/>
       <c r="L4" s="9"/>
       <c r="M4" s="9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="N4" s="9"/>
     </row>
@@ -5403,32 +5267,32 @@
         <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5" s="8">
         <v>40</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>48</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>49</v>
       </c>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N5" s="9"/>
     </row>
@@ -5437,23 +5301,23 @@
         <v>13</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" s="8">
         <v>50</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
       <c r="J6" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
@@ -5465,34 +5329,34 @@
         <v>14</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="8">
         <v>20</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
       <c r="M7" s="9" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="N7" s="9"/>
     </row>
@@ -5501,34 +5365,34 @@
         <v>15</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" s="8">
         <v>3</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="K8" s="9"/>
       <c r="L8" s="9"/>
       <c r="M8" s="9" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="N8" s="9"/>
     </row>
@@ -5537,26 +5401,26 @@
         <v>16</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" s="8">
         <v>5</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
@@ -5569,100 +5433,96 @@
         <v>17</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C10" s="8">
         <v>3</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K10" s="9"/>
       <c r="L10" s="9"/>
       <c r="M10" s="9"/>
       <c r="N10" s="9"/>
     </row>
-    <row r="11" spans="1:14" ht="72" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="156" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C11" s="8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>79</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="J11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
     </row>
-    <row r="12" spans="1:14" ht="156" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="72" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C12" s="8">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="J12" s="9"/>
+        <v>75</v>
+      </c>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9" t="s">
+        <v>76</v>
+      </c>
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
@@ -5673,34 +5533,34 @@
         <v>20</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C13" s="8">
         <v>25</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
       <c r="J13" s="9" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
       <c r="M13" s="9"/>
       <c r="N13" s="9"/>
     </row>
-    <row r="14" spans="1:14" ht="72" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>21</v>
       </c>
@@ -5708,112 +5568,108 @@
         <v>52</v>
       </c>
       <c r="C14" s="8">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>80</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="F14" s="7"/>
+      <c r="G14" s="9"/>
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
       <c r="J14" s="9" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="K14" s="9"/>
       <c r="L14" s="9"/>
       <c r="M14" s="9"/>
       <c r="N14" s="9"/>
     </row>
-    <row r="15" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="96" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C15" s="8">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
+        <v>111</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>78</v>
+      </c>
       <c r="I15" s="9"/>
-      <c r="J15" s="9" t="s">
-        <v>82</v>
-      </c>
+      <c r="J15" s="9"/>
       <c r="K15" s="9"/>
       <c r="L15" s="9"/>
       <c r="M15" s="9"/>
       <c r="N15" s="9"/>
     </row>
-    <row r="16" spans="1:14" ht="96" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="204" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C16" s="8">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>83</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="F16" s="7"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
       <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
+      <c r="J16" s="9" t="s">
+        <v>128</v>
+      </c>
       <c r="K16" s="9"/>
       <c r="L16" s="9"/>
       <c r="M16" s="9"/>
       <c r="N16" s="9"/>
     </row>
-    <row r="17" spans="1:14" ht="204" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>24</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C17" s="8">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
       <c r="J17" s="9" t="s">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="9"/>
@@ -5825,186 +5681,192 @@
         <v>25</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="8">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="9"/>
       <c r="J18" s="9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
       <c r="M18" s="9"/>
       <c r="N18" s="9"/>
     </row>
-    <row r="19" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="180" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C19" s="8">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
       <c r="J19" s="9" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="K19" s="9"/>
       <c r="L19" s="9"/>
       <c r="M19" s="9"/>
       <c r="N19" s="9"/>
     </row>
-    <row r="20" spans="1:14" ht="180" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="36" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="8">
-        <v>25</v>
+        <v>43</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="F20" s="7"/>
+        <v>112</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>111</v>
+      </c>
       <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9" t="s">
-        <v>135</v>
-      </c>
+      <c r="H20" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J20" s="9"/>
       <c r="K20" s="9"/>
       <c r="L20" s="9"/>
       <c r="M20" s="9"/>
       <c r="N20" s="9"/>
     </row>
-    <row r="21" spans="1:14" ht="36" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="72" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>28</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>59</v>
+        <v>43</v>
+      </c>
+      <c r="C21" s="7">
+        <v>0</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G21" s="9"/>
       <c r="H21" s="9" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="J21" s="9"/>
+        <v>82</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>83</v>
+      </c>
       <c r="K21" s="9"/>
       <c r="L21" s="9"/>
       <c r="M21" s="9"/>
       <c r="N21" s="9"/>
     </row>
-    <row r="22" spans="1:14" ht="72" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="108" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C22" s="7">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G22" s="9"/>
       <c r="H22" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="J22" s="9" t="s">
         <v>86</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>88</v>
       </c>
       <c r="K22" s="9"/>
       <c r="L22" s="9"/>
       <c r="M22" s="9"/>
       <c r="N22" s="9"/>
     </row>
-    <row r="23" spans="1:14" ht="108" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="132" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>30</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C23" s="7">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G23" s="9"/>
       <c r="H23" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="J23" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>91</v>
       </c>
       <c r="K23" s="9"/>
       <c r="L23" s="9"/>
       <c r="M23" s="9"/>
       <c r="N23" s="9"/>
     </row>
-    <row r="24" spans="1:14" ht="132" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="108" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>31</v>
       </c>
@@ -6015,54 +5877,52 @@
         <v>0</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E24" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="F24" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>94</v>
-      </c>
+      <c r="H24" s="9"/>
+      <c r="I24" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="J24" s="9"/>
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
       <c r="M24" s="9"/>
       <c r="N24" s="9"/>
     </row>
-    <row r="25" spans="1:14" ht="108" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="72" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>32</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="7">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
@@ -6075,187 +5935,189 @@
         <v>33</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>60</v>
+        <v>43</v>
+      </c>
+      <c r="C26" s="7">
+        <v>20</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H26" s="9"/>
-      <c r="I26" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="J26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="K26" s="9"/>
       <c r="L26" s="9"/>
       <c r="M26" s="9"/>
       <c r="N26" s="9"/>
     </row>
-    <row r="27" spans="1:14" ht="72" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="7">
-        <v>20</v>
+        <v>51</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="H27" s="9"/>
+        <v>112</v>
+      </c>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9" t="s">
+        <v>60</v>
+      </c>
       <c r="I27" s="9"/>
       <c r="J27" s="9" t="s">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="K27" s="9"/>
       <c r="L27" s="9"/>
       <c r="M27" s="9"/>
       <c r="N27" s="9"/>
     </row>
-    <row r="28" spans="1:14" ht="48" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="36" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>117</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="F28" s="7"/>
       <c r="G28" s="9"/>
-      <c r="H28" s="9" t="s">
-        <v>63</v>
-      </c>
+      <c r="H28" s="9"/>
       <c r="I28" s="9"/>
       <c r="J28" s="9" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="K28" s="9"/>
       <c r="L28" s="9"/>
       <c r="M28" s="9"/>
       <c r="N28" s="9"/>
     </row>
-    <row r="29" spans="1:14" ht="36" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="108" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>36</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="F29" s="7"/>
+        <v>110</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>112</v>
+      </c>
       <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
+      <c r="H29" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>96</v>
+      </c>
       <c r="J29" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K29" s="9"/>
       <c r="L29" s="9"/>
       <c r="M29" s="9"/>
       <c r="N29" s="9"/>
     </row>
-    <row r="30" spans="1:14" ht="108" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="96" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>37</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G30" s="9"/>
       <c r="H30" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="J30" s="9" t="s">
         <v>100</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="J30" s="9" t="s">
-        <v>102</v>
       </c>
       <c r="K30" s="9"/>
       <c r="L30" s="9"/>
       <c r="M30" s="9"/>
       <c r="N30" s="9"/>
     </row>
-    <row r="31" spans="1:14" ht="96" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="144" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>38</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G31" s="9"/>
       <c r="H31" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="J31" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="J31" s="9" t="s">
-        <v>105</v>
       </c>
       <c r="K31" s="9"/>
       <c r="L31" s="9"/>
@@ -6267,101 +6129,67 @@
         <v>39</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G32" s="9"/>
       <c r="H32" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="J32" s="9" t="s">
         <v>106</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>108</v>
       </c>
       <c r="K32" s="9"/>
       <c r="L32" s="9"/>
       <c r="M32" s="9"/>
       <c r="N32" s="9"/>
     </row>
-    <row r="33" spans="1:14" ht="144" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" ht="84" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9" t="s">
-        <v>109</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="H33" s="9"/>
       <c r="I33" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>111</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="J33" s="9"/>
       <c r="K33" s="9"/>
       <c r="L33" s="9"/>
       <c r="M33" s="9"/>
       <c r="N33" s="9"/>
     </row>
-    <row r="34" spans="1:14" ht="84" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/FieldConfigrationFile.xlsx
+++ b/FieldConfigrationFile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prakhar\Desktop\Projects\IMGC Project\Field Level Mapping Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A164DB-53E2-4CA1-A94A-BC4C3F14AC50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{93AC75CB-B4E8-47B0-BD3A-84F291FC0D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{02CFE6FC-DC13-4DF7-B179-54CE07624848}"/>
   </bookViews>
@@ -315,95 +315,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">It can be obtained from the Application Form under the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Sourcing Channel Details</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> section, in the field </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Location Name.”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The value for this field should be mapped based on the corresponding </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>City</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Branch</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">In the PD document, the sourcing city is generally referenced within the </t>
     </r>
     <r>
@@ -4636,6 +4547,53 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> or similar areas, look for keywords like "having cash salary" or comparable phrases/statements. Analyze these to determine whether the salary mode is cash or SALARY REFLECTED IN BANK.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">It can be obtained from the Application Form under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sourcing Channel Details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> section, in the field </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Location Name.”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
     </r>
   </si>
 </sst>
@@ -5180,10 +5138,10 @@
         <v>62</v>
       </c>
       <c r="E2" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>109</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>110</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
@@ -5200,7 +5158,7 @@
       </c>
       <c r="N2" s="9"/>
     </row>
-    <row r="3" spans="1:14" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" s="5" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>10</v>
       </c>
@@ -5214,14 +5172,14 @@
         <v>62</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
       <c r="J3" s="9" t="s">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
@@ -5242,23 +5200,23 @@
         <v>62</v>
       </c>
       <c r="E4" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>109</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>110</v>
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
       <c r="I4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="J4" s="9" t="s">
         <v>69</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>70</v>
       </c>
       <c r="K4" s="9"/>
       <c r="L4" s="9"/>
       <c r="M4" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N4" s="9"/>
     </row>
@@ -5276,10 +5234,10 @@
         <v>62</v>
       </c>
       <c r="E5" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>109</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>110</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
@@ -5310,7 +5268,7 @@
         <v>62</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="9"/>
@@ -5338,25 +5296,25 @@
         <v>62</v>
       </c>
       <c r="E7" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>110</v>
-      </c>
       <c r="G7" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="J7" s="9" t="s">
         <v>117</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>118</v>
       </c>
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
       <c r="M7" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N7" s="9"/>
     </row>
@@ -5374,25 +5332,25 @@
         <v>62</v>
       </c>
       <c r="E8" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>110</v>
-      </c>
       <c r="G8" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="J8" s="9" t="s">
         <v>121</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>122</v>
       </c>
       <c r="K8" s="9"/>
       <c r="L8" s="9"/>
       <c r="M8" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N8" s="9"/>
     </row>
@@ -5410,17 +5368,17 @@
         <v>62</v>
       </c>
       <c r="E9" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>112</v>
-      </c>
       <c r="G9" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
@@ -5442,20 +5400,20 @@
         <v>62</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>112</v>
-      </c>
       <c r="G10" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="J10" s="9" t="s">
         <v>73</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>74</v>
       </c>
       <c r="K10" s="9"/>
       <c r="L10" s="9"/>
@@ -5476,19 +5434,19 @@
         <v>62</v>
       </c>
       <c r="E11" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>112</v>
-      </c>
       <c r="G11" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="I11" s="9" t="s">
         <v>126</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>127</v>
       </c>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
@@ -5510,18 +5468,18 @@
         <v>62</v>
       </c>
       <c r="E12" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>111</v>
-      </c>
       <c r="G12" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
       <c r="J12" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
@@ -5542,18 +5500,18 @@
         <v>62</v>
       </c>
       <c r="E13" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>111</v>
-      </c>
       <c r="G13" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
       <c r="J13" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
@@ -5574,14 +5532,14 @@
         <v>62</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
       <c r="J14" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K14" s="9"/>
       <c r="L14" s="9"/>
@@ -5602,16 +5560,16 @@
         <v>62</v>
       </c>
       <c r="E15" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="G15" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G15" s="9" t="s">
-        <v>113</v>
-      </c>
       <c r="H15" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
@@ -5634,14 +5592,14 @@
         <v>63</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
       <c r="I16" s="9"/>
       <c r="J16" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K16" s="9"/>
       <c r="L16" s="9"/>
@@ -5662,14 +5620,14 @@
         <v>62</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
       <c r="J17" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="9"/>
@@ -5690,14 +5648,14 @@
         <v>62</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="9"/>
       <c r="J18" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
@@ -5718,14 +5676,14 @@
         <v>62</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
       <c r="J19" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K19" s="9"/>
       <c r="L19" s="9"/>
@@ -5746,10 +5704,10 @@
         <v>62</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G20" s="9"/>
       <c r="H20" s="9" t="s">
@@ -5778,20 +5736,20 @@
         <v>62</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G21" s="9"/>
       <c r="H21" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="J21" s="9" t="s">
         <v>82</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>83</v>
       </c>
       <c r="K21" s="9"/>
       <c r="L21" s="9"/>
@@ -5812,20 +5770,20 @@
         <v>62</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G22" s="9"/>
       <c r="H22" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I22" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="I22" s="9" t="s">
+      <c r="J22" s="9" t="s">
         <v>85</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>86</v>
       </c>
       <c r="K22" s="9"/>
       <c r="L22" s="9"/>
@@ -5846,20 +5804,20 @@
         <v>62</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G23" s="9"/>
       <c r="H23" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I23" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="I23" s="9" t="s">
+      <c r="J23" s="9" t="s">
         <v>88</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>89</v>
       </c>
       <c r="K23" s="9"/>
       <c r="L23" s="9"/>
@@ -5880,17 +5838,17 @@
         <v>63</v>
       </c>
       <c r="E24" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F24" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="F24" s="7" t="s">
-        <v>112</v>
-      </c>
       <c r="G24" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H24" s="9"/>
       <c r="I24" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
@@ -5912,17 +5870,17 @@
         <v>63</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
@@ -5944,18 +5902,18 @@
         <v>62</v>
       </c>
       <c r="E26" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F26" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F26" s="7" t="s">
-        <v>111</v>
-      </c>
       <c r="G26" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H26" s="9"/>
       <c r="I26" s="9"/>
       <c r="J26" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K26" s="9"/>
       <c r="L26" s="9"/>
@@ -5976,10 +5934,10 @@
         <v>62</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G27" s="9"/>
       <c r="H27" s="9" t="s">
@@ -6008,14 +5966,14 @@
         <v>62</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
       <c r="J28" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K28" s="9"/>
       <c r="L28" s="9"/>
@@ -6036,20 +5994,20 @@
         <v>62</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G29" s="9"/>
       <c r="H29" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="I29" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="I29" s="9" t="s">
+      <c r="J29" s="9" t="s">
         <v>96</v>
-      </c>
-      <c r="J29" s="9" t="s">
-        <v>97</v>
       </c>
       <c r="K29" s="9"/>
       <c r="L29" s="9"/>
@@ -6070,20 +6028,20 @@
         <v>63</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G30" s="9"/>
       <c r="H30" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="I30" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="I30" s="9" t="s">
+      <c r="J30" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="J30" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="K30" s="9"/>
       <c r="L30" s="9"/>
@@ -6104,20 +6062,20 @@
         <v>62</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G31" s="9"/>
       <c r="H31" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="I31" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="I31" s="9" t="s">
+      <c r="J31" s="9" t="s">
         <v>102</v>
-      </c>
-      <c r="J31" s="9" t="s">
-        <v>103</v>
       </c>
       <c r="K31" s="9"/>
       <c r="L31" s="9"/>
@@ -6138,20 +6096,20 @@
         <v>62</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G32" s="9"/>
       <c r="H32" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="I32" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="I32" s="9" t="s">
+      <c r="J32" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="K32" s="9"/>
       <c r="L32" s="9"/>
@@ -6172,17 +6130,17 @@
         <v>63</v>
       </c>
       <c r="E33" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F33" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="F33" s="7" t="s">
-        <v>112</v>
-      </c>
       <c r="G33" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H33" s="9"/>
       <c r="I33" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
